--- a/pasta_verificador.xlsx
+++ b/pasta_verificador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20343"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\VERIFICADOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8009478-1D6A-4A07-B57E-DB851E67FD43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876A35F3-83E4-4586-AF15-8B1B0C1F5417}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{37095C7E-84E9-487F-AA21-A432EC8D61AA}"/>
   </bookViews>
@@ -117,7 +117,7 @@
     <t>TESTANDO MÉDIA MAIOR QUE 10</t>
   </si>
   <si>
-    <t>ValueError:"O VALOR DEVE SER MAIOR QUE OU IGUAL A 0 E MENOR OU IGUAL A 11</t>
+    <t>ValueError:"O VALOR DEVE SER MAIOR  OU IGUAL A 0 E MENOR OU IGUAL A 10</t>
   </si>
 </sst>
 </file>
@@ -222,33 +222,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{564EB83A-E465-4352-9404-364108917FAD}" name="Tabela3" displayName="Tabela3" ref="A1:F9" totalsRowShown="0" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{564EB83A-E465-4352-9404-364108917FAD}" name="Tabela3" displayName="Tabela3" ref="A1:F9" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A1:F9" xr:uid="{85E3052B-094B-499B-880B-7CD054D2B2DE}"/>
   <sortState ref="A2:F9">
     <sortCondition ref="A1:A9"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DB555BB5-6B2C-4D15-BF44-ADA46C5A66DB}" name="TIPO DE TESTE" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{E8A019A2-F998-4A6E-A7DE-1917D7C6D52D}" name="ARQUIVOS" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{8BBD2BCE-C3D4-4674-8ECE-7C6BFC3C55D0}" name="FUNÇÕES" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{F4BA9010-100D-4B49-A4CB-EEE0933CB532}" name="TESTE" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{C7265628-4825-4EF3-BCA9-3B7ACAEAD892}" name="ENTRADA" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{05FE90D9-1739-42C1-8BCB-F760AD7D05EB}" name="SAÍDA" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{DB555BB5-6B2C-4D15-BF44-ADA46C5A66DB}" name="TIPO DE TESTE" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{E8A019A2-F998-4A6E-A7DE-1917D7C6D52D}" name="ARQUIVOS" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{8BBD2BCE-C3D4-4674-8ECE-7C6BFC3C55D0}" name="FUNÇÕES" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{F4BA9010-100D-4B49-A4CB-EEE0933CB532}" name="TESTE" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{C7265628-4825-4EF3-BCA9-3B7ACAEAD892}" name="ENTRADA" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{05FE90D9-1739-42C1-8BCB-F760AD7D05EB}" name="SAÍDA" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{77AECBAD-3D3A-460C-96EF-F4748A6016BF}" name="Tabela4" displayName="Tabela4" ref="A14:F17" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{77AECBAD-3D3A-460C-96EF-F4748A6016BF}" name="Tabela4" displayName="Tabela4" ref="A14:F17" totalsRowShown="0" dataDxfId="6">
   <autoFilter ref="A14:F17" xr:uid="{BC169861-76BF-4784-BF55-255526911F79}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{332E1484-96FE-42E5-84F8-2E545B8E09B4}" name="TIPOS DE TESTE" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{7EF4C8D7-BEC9-4656-ACAD-2E80C8923DBC}" name="ARQUIVOS" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B5F17FDE-52CE-4D0D-A6C7-67D30F82CD79}" name="FUNÇÕES" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{212F87D8-5108-4EC4-A46C-B2626EC6879E}" name="TESTE" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{81108EDA-0960-4DD2-ADD0-93A89B2348AD}" name="ENTRADA" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{E6AE48D0-B52C-4EFC-B2C8-0AC0F17A4A3F}" name="SAÍDA" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{332E1484-96FE-42E5-84F8-2E545B8E09B4}" name="TIPOS DE TESTE" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7EF4C8D7-BEC9-4656-ACAD-2E80C8923DBC}" name="ARQUIVOS" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B5F17FDE-52CE-4D0D-A6C7-67D30F82CD79}" name="FUNÇÕES" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{212F87D8-5108-4EC4-A46C-B2626EC6879E}" name="TESTE" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{81108EDA-0960-4DD2-ADD0-93A89B2348AD}" name="ENTRADA" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E6AE48D0-B52C-4EFC-B2C8-0AC0F17A4A3F}" name="SAÍDA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -809,7 +809,7 @@
         <v>-5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -829,7 +829,7 @@
         <v>2000</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
